--- a/data/05_modelado/results/results_ensambles.xlsx
+++ b/data/05_modelado/results/results_ensambles.xlsx
@@ -568,7 +568,7 @@
         <v>0.9012862840552307</v>
       </c>
       <c r="K2" t="n">
-        <v>1390.184</v>
+        <v>2051.132</v>
       </c>
       <c r="L2" t="n">
         <v>6.83</v>
@@ -636,7 +636,7 @@
         <v>0.9012862840552307</v>
       </c>
       <c r="K3" t="n">
-        <v>1442.575</v>
+        <v>525.189</v>
       </c>
       <c r="L3" t="n">
         <v>6.68</v>
@@ -704,10 +704,10 @@
         <v>0.8955233038299155</v>
       </c>
       <c r="K4" t="n">
-        <v>6342.906</v>
+        <v>1805.924</v>
       </c>
       <c r="L4" t="n">
-        <v>6.68</v>
+        <v>6.69</v>
       </c>
       <c r="M4" t="n">
         <v>0.8196</v>
@@ -772,10 +772,10 @@
         <v>0.895523366029672</v>
       </c>
       <c r="K5" t="n">
-        <v>656.528</v>
+        <v>229.459</v>
       </c>
       <c r="L5" t="n">
-        <v>6.94</v>
+        <v>6.95</v>
       </c>
       <c r="M5" t="n">
         <v>0.8176</v>
@@ -840,10 +840,10 @@
         <v>0.895523366029672</v>
       </c>
       <c r="K6" t="n">
-        <v>481.012</v>
+        <v>117.023</v>
       </c>
       <c r="L6" t="n">
-        <v>6.67</v>
+        <v>6.69</v>
       </c>
       <c r="M6" t="n">
         <v>0.8176</v>
@@ -908,7 +908,7 @@
         <v>0.8940361352941461</v>
       </c>
       <c r="K7" t="n">
-        <v>1731.173</v>
+        <v>1386.375</v>
       </c>
       <c r="L7" t="n">
         <v>6.67</v>
@@ -976,7 +976,7 @@
         <v>0.8692367882533686</v>
       </c>
       <c r="K8" t="n">
-        <v>71.434</v>
+        <v>15.005</v>
       </c>
       <c r="L8" t="n">
         <v>6.64</v>
@@ -1044,7 +1044,7 @@
         <v>0.8738103778220548</v>
       </c>
       <c r="K9" t="n">
-        <v>20.731</v>
+        <v>5.371</v>
       </c>
       <c r="L9" t="n">
         <v>6.8</v>
@@ -1112,7 +1112,7 @@
         <v>0.8738103778220548</v>
       </c>
       <c r="K10" t="n">
-        <v>18.024</v>
+        <v>2.148</v>
       </c>
       <c r="L10" t="n">
         <v>6.64</v>
@@ -1180,10 +1180,10 @@
         <v>0.8680099187878512</v>
       </c>
       <c r="K11" t="n">
-        <v>31.611</v>
+        <v>7.129</v>
       </c>
       <c r="L11" t="n">
-        <v>6.64</v>
+        <v>6.78</v>
       </c>
       <c r="M11" t="n">
         <v>0.7606000000000001</v>
@@ -1248,7 +1248,7 @@
         <v>0.8680099187878512</v>
       </c>
       <c r="K12" t="n">
-        <v>33.396</v>
+        <v>6.983</v>
       </c>
       <c r="L12" t="n">
         <v>6.64</v>
@@ -1316,7 +1316,7 @@
         <v>0.8528036747616194</v>
       </c>
       <c r="K13" t="n">
-        <v>35.549</v>
+        <v>3.993</v>
       </c>
       <c r="L13" t="n">
         <v>6.64</v>
